--- a/data/holding.xlsx
+++ b/data/holding.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dalva\src\project-hail-mary\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC4FCA1-E3E8-4D71-9B54-3F6B031FAAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639C7904-62E6-4364-9805-08629C687371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41850" yWindow="2520" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Holdings" sheetId="1" r:id="rId1"/>
-    <sheet name="PortfolioValueSGD" sheetId="5" r:id="rId2"/>
-    <sheet name="PortfolioValueBase" sheetId="6" r:id="rId3"/>
-    <sheet name="Deposits" sheetId="4" r:id="rId4"/>
+    <sheet name="PortfolioValue" sheetId="6" r:id="rId2"/>
+    <sheet name="Deposits" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Deposits!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Deposits!$A$1:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Holdings!$E$7:$O$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PortfolioValueSGD!$F$6:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PortfolioValue!$F$6:$L$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="238">
   <si>
     <t>Id</t>
   </si>
@@ -556,9 +555,6 @@
     <t>Public Market Investments</t>
   </si>
   <si>
-    <t>CCY</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -740,6 +736,24 @@
   </si>
   <si>
     <t>iShares $ Floating Rate Bond UCITS ETF</t>
+  </si>
+  <si>
+    <t>Base Currency</t>
+  </si>
+  <si>
+    <t>4/30/2026 (Base)</t>
+  </si>
+  <si>
+    <t>5/31/2026 (Base)</t>
+  </si>
+  <si>
+    <t>4/30/2026 (SGD)</t>
+  </si>
+  <si>
+    <t>5/31/2026 (SGD)</t>
+  </si>
+  <si>
+    <t>FX Rate to base</t>
   </si>
 </sst>
 </file>
@@ -754,7 +768,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -889,10 +903,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -923,7 +970,7 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -976,18 +1023,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1385,7 +1438,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>4</v>
@@ -1407,7 +1460,7 @@
       <c r="Q7" s="2"/>
       <c r="W7" s="3"/>
     </row>
-    <row r="8" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="1">
         <v>1</v>
       </c>
@@ -1419,7 +1472,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>16</v>
@@ -1437,7 +1490,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E9" s="1">
         <v>1</v>
       </c>
@@ -1449,7 +1502,7 @@
         <v>18</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>16</v>
@@ -1467,7 +1520,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="10" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E10" s="1">
         <v>1</v>
       </c>
@@ -1479,7 +1532,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>21</v>
@@ -1497,7 +1550,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="11" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="1">
         <v>1</v>
       </c>
@@ -1509,7 +1562,7 @@
         <v>23</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>24</v>
@@ -1527,7 +1580,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="1">
         <v>1</v>
       </c>
@@ -1539,7 +1592,7 @@
         <v>26</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>27</v>
@@ -1557,7 +1610,7 @@
         <v>0.16200000000000001</v>
       </c>
     </row>
-    <row r="13" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="1">
         <v>1</v>
       </c>
@@ -1569,7 +1622,7 @@
         <v>29</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>30</v>
@@ -1587,7 +1640,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="14" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" s="1">
         <v>1</v>
       </c>
@@ -1599,7 +1652,7 @@
         <v>32</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>33</v>
@@ -1617,7 +1670,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E15" s="1">
         <v>1</v>
       </c>
@@ -1629,7 +1682,7 @@
         <v>35</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>30</v>
@@ -1647,7 +1700,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" s="1">
         <v>1</v>
       </c>
@@ -1659,7 +1712,7 @@
         <v>37</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>21</v>
@@ -1677,7 +1730,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E17" s="1">
         <v>1</v>
       </c>
@@ -1689,7 +1742,7 @@
         <v>39</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>27</v>
@@ -1708,7 +1761,7 @@
       </c>
       <c r="Z17" s="4"/>
     </row>
-    <row r="18" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E18" s="1">
         <v>1</v>
       </c>
@@ -1720,7 +1773,7 @@
         <v>41</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>42</v>
@@ -1738,7 +1791,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E19" s="1">
         <v>1</v>
       </c>
@@ -1750,7 +1803,7 @@
         <v>44</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>33</v>
@@ -1768,7 +1821,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E20" s="1">
         <v>1</v>
       </c>
@@ -1780,7 +1833,7 @@
         <v>46</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>47</v>
@@ -1798,7 +1851,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="21" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E21" s="1">
         <v>1</v>
       </c>
@@ -1810,7 +1863,7 @@
         <v>49</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>33</v>
@@ -1828,7 +1881,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="22" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E22" s="1">
         <v>1</v>
       </c>
@@ -1840,7 +1893,7 @@
         <v>51</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>52</v>
@@ -1858,7 +1911,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E23" s="1">
         <v>1</v>
       </c>
@@ -1870,7 +1923,7 @@
         <v>54</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>33</v>
@@ -1888,7 +1941,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E24" s="1">
         <v>1</v>
       </c>
@@ -1900,7 +1953,7 @@
         <v>10</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>11</v>
@@ -1918,7 +1971,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="25" spans="5:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:26" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E25" s="1">
         <v>1</v>
       </c>
@@ -1930,7 +1983,7 @@
         <v>13</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>11</v>
@@ -2010,7 +2063,7 @@
         <v>51</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>52</v>
@@ -2040,7 +2093,7 @@
         <v>59</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>52</v>
@@ -2120,7 +2173,7 @@
         <v>63</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>47</v>
@@ -2150,7 +2203,7 @@
         <v>65</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>33</v>
@@ -2205,7 +2258,7 @@
         <v>68</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>69</v>
@@ -2235,7 +2288,7 @@
         <v>71</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>69</v>
@@ -2265,7 +2318,7 @@
         <v>73</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>27</v>
@@ -2319,7 +2372,7 @@
         <v>13</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>11</v>
@@ -2360,7 +2413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E41" s="1">
         <v>8</v>
       </c>
@@ -2371,7 +2424,7 @@
         <v>106</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>27</v>
@@ -2389,7 +2442,7 @@
         <v>1.09E-2</v>
       </c>
     </row>
-    <row r="42" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E42" s="1">
         <v>8</v>
       </c>
@@ -2400,7 +2453,7 @@
         <v>85</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>27</v>
@@ -2418,7 +2471,7 @@
         <v>4.1599999999999998E-2</v>
       </c>
     </row>
-    <row r="43" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="1">
         <v>8</v>
       </c>
@@ -2429,7 +2482,7 @@
         <v>75</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>30</v>
@@ -2447,7 +2500,7 @@
         <v>0.1832</v>
       </c>
     </row>
-    <row r="44" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E44" s="1">
         <v>8</v>
       </c>
@@ -2458,7 +2511,7 @@
         <v>77</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>30</v>
@@ -2479,7 +2532,7 @@
       <c r="U44" s="18"/>
       <c r="W44" s="19"/>
     </row>
-    <row r="45" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E45" s="1">
         <v>8</v>
       </c>
@@ -2490,7 +2543,7 @@
         <v>79</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>30</v>
@@ -2510,7 +2563,7 @@
       <c r="S45" s="17"/>
       <c r="U45" s="18"/>
     </row>
-    <row r="46" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E46" s="1">
         <v>8</v>
       </c>
@@ -2521,7 +2574,7 @@
         <v>81</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>27</v>
@@ -2541,7 +2594,7 @@
       <c r="S46" s="17"/>
       <c r="U46" s="18"/>
     </row>
-    <row r="47" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E47" s="1">
         <v>8</v>
       </c>
@@ -2552,7 +2605,7 @@
         <v>83</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>27</v>
@@ -2572,7 +2625,7 @@
       <c r="S47" s="17"/>
       <c r="U47" s="18"/>
     </row>
-    <row r="48" spans="5:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:23" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E48" s="1">
         <v>8</v>
       </c>
@@ -2583,7 +2636,7 @@
         <v>26</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>27</v>
@@ -2603,7 +2656,7 @@
       <c r="S48" s="17"/>
       <c r="U48" s="18"/>
     </row>
-    <row r="49" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E49" s="1">
         <v>8</v>
       </c>
@@ -2614,7 +2667,7 @@
         <v>86</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>87</v>
@@ -2634,7 +2687,7 @@
       <c r="S49" s="17"/>
       <c r="U49" s="18"/>
     </row>
-    <row r="50" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E50" s="1">
         <v>8</v>
       </c>
@@ -2645,7 +2698,7 @@
         <v>89</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>90</v>
@@ -2663,7 +2716,7 @@
         <v>3.6600000000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E51" s="1">
         <v>8</v>
       </c>
@@ -2674,7 +2727,7 @@
         <v>92</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>27</v>
@@ -2692,7 +2745,7 @@
         <v>3.27E-2</v>
       </c>
     </row>
-    <row r="52" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E52" s="1">
         <v>8</v>
       </c>
@@ -2703,7 +2756,7 @@
         <v>94</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>24</v>
@@ -2721,7 +2774,7 @@
         <v>2.7699999999999999E-2</v>
       </c>
     </row>
-    <row r="53" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E53" s="1">
         <v>8</v>
       </c>
@@ -2732,7 +2785,7 @@
         <v>96</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>21</v>
@@ -2750,7 +2803,7 @@
         <v>2.7699999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E54" s="1">
         <v>8</v>
       </c>
@@ -2761,7 +2814,7 @@
         <v>98</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>90</v>
@@ -2779,7 +2832,7 @@
         <v>2.6700000000000002E-2</v>
       </c>
     </row>
-    <row r="55" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E55" s="1">
         <v>8</v>
       </c>
@@ -2790,7 +2843,7 @@
         <v>100</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>90</v>
@@ -2808,7 +2861,7 @@
         <v>1.8800000000000001E-2</v>
       </c>
     </row>
-    <row r="56" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E56" s="1">
         <v>8</v>
       </c>
@@ -2819,7 +2872,7 @@
         <v>102</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>90</v>
@@ -2837,7 +2890,7 @@
         <v>1.4800000000000001E-2</v>
       </c>
     </row>
-    <row r="57" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E57" s="1">
         <v>8</v>
       </c>
@@ -2848,7 +2901,7 @@
         <v>104</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>27</v>
@@ -2866,7 +2919,7 @@
         <v>1.09E-2</v>
       </c>
     </row>
-    <row r="58" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E58" s="1">
         <v>8</v>
       </c>
@@ -2877,7 +2930,7 @@
         <v>109</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>30</v>
@@ -2895,7 +2948,7 @@
         <v>9.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="59" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E59" s="1">
         <v>8</v>
       </c>
@@ -2906,7 +2959,7 @@
         <v>110</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>90</v>
@@ -2924,7 +2977,7 @@
         <v>7.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="60" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E60" s="1">
         <v>8</v>
       </c>
@@ -2935,7 +2988,7 @@
         <v>89</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>112</v>
@@ -2953,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E61" s="1">
         <v>8</v>
       </c>
@@ -2964,7 +3017,7 @@
         <v>100</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>112</v>
@@ -2982,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="5:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="5:21" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E62" s="1">
         <v>8</v>
       </c>
@@ -2993,7 +3046,7 @@
         <v>107</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>27</v>
@@ -3045,7 +3098,7 @@
         <v>39</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>27</v>
@@ -3074,7 +3127,7 @@
         <v>114</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>30</v>
@@ -3103,7 +3156,7 @@
         <v>116</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>47</v>
@@ -3178,7 +3231,7 @@
         <v>118</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>11</v>
@@ -3219,7 +3272,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="71" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E71" s="1">
         <v>13</v>
       </c>
@@ -3230,7 +3283,7 @@
         <v>121</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>122</v>
@@ -3248,7 +3301,7 @@
         <v>0.28710000000000002</v>
       </c>
     </row>
-    <row r="72" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E72" s="1">
         <v>13</v>
       </c>
@@ -3259,7 +3312,7 @@
         <v>124</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>122</v>
@@ -3277,7 +3330,7 @@
         <v>0.28710000000000002</v>
       </c>
     </row>
-    <row r="73" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E73" s="1">
         <v>13</v>
       </c>
@@ -3288,7 +3341,7 @@
         <v>126</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>38</v>
@@ -3306,7 +3359,7 @@
         <v>0.16830000000000001</v>
       </c>
     </row>
-    <row r="74" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E74" s="1">
         <v>13</v>
       </c>
@@ -3317,7 +3370,7 @@
         <v>127</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>128</v>
@@ -3335,7 +3388,7 @@
         <v>0.14849999999999999</v>
       </c>
     </row>
-    <row r="75" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E75" s="1">
         <v>13</v>
       </c>
@@ -3346,7 +3399,7 @@
         <v>130</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>131</v>
@@ -3375,7 +3428,7 @@
         <v>134</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>33</v>
@@ -3416,7 +3469,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="78" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E78" s="1">
         <v>15</v>
       </c>
@@ -3427,7 +3480,7 @@
         <v>136</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>137</v>
@@ -3445,7 +3498,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="79" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E79" s="1">
         <v>15</v>
       </c>
@@ -3456,7 +3509,7 @@
         <v>68</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>69</v>
@@ -3474,7 +3527,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="80" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E80" s="1">
         <v>15</v>
       </c>
@@ -3485,7 +3538,7 @@
         <v>118</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>11</v>
@@ -3503,7 +3556,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="81" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E81" s="1">
         <v>15</v>
       </c>
@@ -3514,7 +3567,7 @@
         <v>139</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>69</v>
@@ -3532,7 +3585,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="82" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E82" s="1">
         <v>15</v>
       </c>
@@ -3543,7 +3596,7 @@
         <v>141</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>142</v>
@@ -3561,7 +3614,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="83" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E83" s="1">
         <v>15</v>
       </c>
@@ -3572,7 +3625,7 @@
         <v>144</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>145</v>
@@ -3601,7 +3654,7 @@
         <v>148</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>142</v>
@@ -3630,7 +3683,7 @@
         <v>41</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>42</v>
@@ -3682,7 +3735,7 @@
         <v>15</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>16</v>
@@ -3711,7 +3764,7 @@
         <v>18</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>16</v>
@@ -3752,7 +3805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E90" s="1">
         <v>19</v>
       </c>
@@ -3764,7 +3817,7 @@
         <v>10</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>11</v>
@@ -3782,7 +3835,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="91" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E91" s="1">
         <v>19</v>
       </c>
@@ -3794,7 +3847,7 @@
         <v>13</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>11</v>
@@ -3812,7 +3865,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="92" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E92" s="1">
         <v>19</v>
       </c>
@@ -3824,7 +3877,7 @@
         <v>15</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>16</v>
@@ -3840,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E93" s="1">
         <v>19</v>
       </c>
@@ -3852,7 +3905,7 @@
         <v>18</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>16</v>
@@ -3868,7 +3921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E94" s="1">
         <v>19</v>
       </c>
@@ -3880,7 +3933,7 @@
         <v>20</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>21</v>
@@ -3898,7 +3951,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="95" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E95" s="1">
         <v>19</v>
       </c>
@@ -3910,7 +3963,7 @@
         <v>23</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>24</v>
@@ -3928,7 +3981,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="96" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E96" s="1">
         <v>19</v>
       </c>
@@ -3940,7 +3993,7 @@
         <v>26</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>27</v>
@@ -3958,7 +4011,7 @@
         <v>0.185</v>
       </c>
     </row>
-    <row r="97" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E97" s="1">
         <v>19</v>
       </c>
@@ -3970,7 +4023,7 @@
         <v>29</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>30</v>
@@ -3988,7 +4041,7 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="98" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E98" s="1">
         <v>19</v>
       </c>
@@ -4000,7 +4053,7 @@
         <v>32</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>33</v>
@@ -4018,7 +4071,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="99" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E99" s="1">
         <v>19</v>
       </c>
@@ -4030,7 +4083,7 @@
         <v>35</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>30</v>
@@ -4048,7 +4101,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="100" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E100" s="1">
         <v>19</v>
       </c>
@@ -4060,7 +4113,7 @@
         <v>37</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>21</v>
@@ -4078,7 +4131,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="101" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E101" s="1">
         <v>19</v>
       </c>
@@ -4090,7 +4143,7 @@
         <v>39</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>27</v>
@@ -4108,7 +4161,7 @@
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="102" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E102" s="1">
         <v>19</v>
       </c>
@@ -4120,7 +4173,7 @@
         <v>41</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>42</v>
@@ -4138,7 +4191,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="103" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E103" s="1">
         <v>19</v>
       </c>
@@ -4150,7 +4203,7 @@
         <v>44</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>33</v>
@@ -4168,7 +4221,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="104" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E104" s="1">
         <v>19</v>
       </c>
@@ -4180,7 +4233,7 @@
         <v>46</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>47</v>
@@ -4198,7 +4251,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="105" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E105" s="1">
         <v>19</v>
       </c>
@@ -4210,7 +4263,7 @@
         <v>49</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>33</v>
@@ -4228,7 +4281,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="106" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E106" s="1">
         <v>19</v>
       </c>
@@ -4240,7 +4293,7 @@
         <v>51</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>52</v>
@@ -4258,7 +4311,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="107" spans="5:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="5:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E107" s="1">
         <v>19</v>
       </c>
@@ -4270,7 +4323,7 @@
         <v>54</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>33</v>
@@ -4324,7 +4377,7 @@
         <v>153</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>142</v>
@@ -4353,7 +4406,7 @@
         <v>155</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>142</v>
@@ -4382,7 +4435,7 @@
         <v>153</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J111" s="1" t="s">
         <v>142</v>
@@ -4411,7 +4464,7 @@
         <v>155</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>142</v>
@@ -4496,6 +4549,26 @@
     </row>
   </sheetData>
   <autoFilter ref="E7:O112" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Asia ex-Japan"/>
+        <filter val="Crypto"/>
+        <filter val="Energy"/>
+        <filter val="Ex-US Large-cap"/>
+        <filter val="Global Floating Rate USD"/>
+        <filter val="Guitsa"/>
+        <filter val="High Dividend Yield"/>
+        <filter val="Investment-Grade SGD"/>
+        <filter val="Japan Currency-hedged"/>
+        <filter val="Longevity Stack"/>
+        <filter val="Nasdaq Covered Call"/>
+        <filter val="SG ETF"/>
+        <filter val="Simple SGD"/>
+        <filter val="Simple USD"/>
+        <filter val="The AI Power Stack"/>
+        <filter val="Utilities"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="6">
       <filters>
         <filter val="Aerospace &amp; Defense"/>
@@ -4775,795 +4848,647 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED5D522-A34F-425F-A8D2-01DA4E744C0F}">
-  <dimension ref="F4:I49"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82086A02-B839-44CF-B0DE-0C0B01F586C8}">
+  <dimension ref="F4:M48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="9.140625" style="21"/>
-    <col min="6" max="6" width="5.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="21"/>
+    <col min="7" max="7" width="31.85546875" style="34" customWidth="1"/>
+    <col min="8" max="8" width="31.85546875" style="28" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" style="21" customWidth="1"/>
+    <col min="10" max="10" width="20.85546875" style="28" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="H4" s="27"/>
+    <row r="4" spans="6:13" x14ac:dyDescent="0.25">
       <c r="I4" s="27"/>
-    </row>
-    <row r="6" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="K4" s="27"/>
+      <c r="M4" s="27"/>
+    </row>
+    <row r="6" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F6" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="H6" s="28">
-        <v>46142</v>
-      </c>
-      <c r="I6" s="28">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="7" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="H6" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="M6" s="28"/>
+    </row>
+    <row r="7" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F7" s="27">
         <v>1</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="29">
         <v>473055.02</v>
       </c>
-      <c r="I7" s="29">
+      <c r="J7" s="31">
+        <v>371548.08</v>
+      </c>
+      <c r="K7" s="29">
         <v>492821.78</v>
       </c>
-    </row>
-    <row r="8" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L7" s="31">
+        <v>386042.44</v>
+      </c>
+      <c r="M7" s="29"/>
+    </row>
+    <row r="8" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F8" s="27">
         <v>2</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="29">
         <v>69775.100000000006</v>
       </c>
-      <c r="I8" s="29">
+      <c r="J8" s="31">
+        <v>54802.94</v>
+      </c>
+      <c r="K8" s="29">
         <v>65760.13</v>
       </c>
-    </row>
-    <row r="9" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L8" s="31">
+        <v>51511.93</v>
+      </c>
+      <c r="M8" s="29"/>
+    </row>
+    <row r="9" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F9" s="27">
         <v>3</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" s="29">
         <v>10466.950000000001</v>
       </c>
-      <c r="I9" s="29">
+      <c r="J9" s="31">
+        <v>8220.98</v>
+      </c>
+      <c r="K9" s="29">
         <v>9903.75</v>
       </c>
-    </row>
-    <row r="10" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L9" s="31">
+        <v>7757.91</v>
+      </c>
+      <c r="M9" s="29"/>
+    </row>
+    <row r="10" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F10" s="27">
         <v>4</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I10" s="29">
         <v>349108.7</v>
       </c>
-      <c r="I10" s="29">
+      <c r="J10" s="31">
+        <v>274197.84999999998</v>
+      </c>
+      <c r="K10" s="29">
         <v>350771.43</v>
       </c>
-    </row>
-    <row r="11" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L10" s="31">
+        <v>274770.03999999998</v>
+      </c>
+      <c r="M10" s="29"/>
+    </row>
+    <row r="11" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F11" s="27">
         <v>5</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="I11" s="29">
         <v>19979.29</v>
       </c>
-      <c r="I11" s="29">
+      <c r="J11" s="31">
+        <v>19979.29</v>
+      </c>
+      <c r="K11" s="29">
         <v>20142.27</v>
       </c>
-    </row>
-    <row r="12" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L11" s="31">
+        <v>20142.27</v>
+      </c>
+      <c r="M11" s="29"/>
+    </row>
+    <row r="12" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F12" s="27">
         <v>6</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I12" s="29">
         <v>4982.24</v>
       </c>
-      <c r="I12" s="29">
+      <c r="J12" s="31">
+        <v>3913.16</v>
+      </c>
+      <c r="K12" s="29">
         <v>4736.4399999999996</v>
       </c>
-    </row>
-    <row r="13" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L12" s="31">
+        <v>3710.2</v>
+      </c>
+      <c r="M12" s="29"/>
+    </row>
+    <row r="13" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F13" s="27">
         <v>7</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="I13" s="29">
         <v>5015.8500000000004</v>
       </c>
-      <c r="I13" s="29">
+      <c r="J13" s="31">
+        <v>5015.8500000000004</v>
+      </c>
+      <c r="K13" s="29">
         <v>5043.68</v>
       </c>
-    </row>
-    <row r="14" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L13" s="31">
+        <v>5043.68</v>
+      </c>
+      <c r="M13" s="29"/>
+    </row>
+    <row r="14" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F14" s="27">
         <v>8</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="29">
         <v>9864.5400000000009</v>
       </c>
-      <c r="I14" s="29">
+      <c r="J14" s="31">
+        <v>9864.5400000000009</v>
+      </c>
+      <c r="K14" s="29">
         <v>20109.849999999999</v>
       </c>
-    </row>
-    <row r="15" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L14" s="31">
+        <v>20109.849999999999</v>
+      </c>
+      <c r="M14" s="29"/>
+    </row>
+    <row r="15" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F15" s="27">
         <v>9</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I15" s="29">
         <v>10046.530000000001</v>
       </c>
-      <c r="I15" s="29">
+      <c r="J15" s="31">
+        <v>7890.77</v>
+      </c>
+      <c r="K15" s="29">
         <v>10518.43</v>
       </c>
-    </row>
-    <row r="16" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L15" s="31">
+        <v>8239.41</v>
+      </c>
+      <c r="M15" s="29"/>
+    </row>
+    <row r="16" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F16" s="27">
         <v>10</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" s="29">
         <v>30379.43</v>
       </c>
-      <c r="I16" s="29">
+      <c r="J16" s="31">
+        <v>23860.69</v>
+      </c>
+      <c r="K16" s="29">
         <v>30848.11</v>
       </c>
-    </row>
-    <row r="17" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L16" s="31">
+        <v>24164.27</v>
+      </c>
+      <c r="M16" s="29"/>
+    </row>
+    <row r="17" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F17" s="27">
         <v>11</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I17" s="29">
         <v>10012.84</v>
       </c>
-      <c r="I17" s="29">
+      <c r="J17" s="31">
+        <v>7864.31</v>
+      </c>
+      <c r="K17" s="29">
         <v>10421.700000000001</v>
       </c>
-    </row>
-    <row r="18" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L17" s="31">
+        <v>8163.64</v>
+      </c>
+      <c r="M17" s="29"/>
+    </row>
+    <row r="18" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F18" s="27">
         <v>12</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="G18" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I18" s="29">
         <v>49884.05</v>
       </c>
-      <c r="I18" s="29">
+      <c r="J18" s="31">
+        <v>39180.06</v>
+      </c>
+      <c r="K18" s="29">
         <v>52369.31</v>
       </c>
-    </row>
-    <row r="19" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L18" s="31">
+        <v>41022.49</v>
+      </c>
+      <c r="M18" s="29"/>
+    </row>
+    <row r="19" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F19" s="27">
         <v>13</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" s="29">
         <v>0</v>
       </c>
-      <c r="I19" s="29">
+      <c r="J19" s="31">
+        <v>0</v>
+      </c>
+      <c r="K19" s="29">
         <v>10166.32</v>
       </c>
-    </row>
-    <row r="20" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L19" s="31">
+        <v>7963.59</v>
+      </c>
+      <c r="M19" s="29"/>
+    </row>
+    <row r="20" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F20" s="27">
         <v>14</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I20" s="29">
         <v>0</v>
       </c>
-      <c r="I20" s="29">
+      <c r="J20" s="31">
+        <v>0</v>
+      </c>
+      <c r="K20" s="29">
         <v>10464.33</v>
       </c>
-    </row>
-    <row r="21" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L20" s="31">
+        <v>8197.0300000000007</v>
+      </c>
+      <c r="M20" s="29"/>
+    </row>
+    <row r="21" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F21" s="27">
         <v>15</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I21" s="29">
         <v>0</v>
       </c>
-      <c r="I21" s="29">
+      <c r="J21" s="31">
+        <v>0</v>
+      </c>
+      <c r="K21" s="29">
         <v>9936.3700000000008</v>
       </c>
-    </row>
-    <row r="22" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L21" s="31">
+        <v>7783.46</v>
+      </c>
+      <c r="M21" s="29"/>
+    </row>
+    <row r="22" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F22" s="27">
         <v>16</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="29">
         <v>0</v>
       </c>
-      <c r="I22" s="29">
+      <c r="J22" s="31">
+        <v>0</v>
+      </c>
+      <c r="K22" s="29">
         <v>9988.9500000000007</v>
       </c>
-    </row>
-    <row r="23" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L22" s="31">
+        <v>9988.9500000000007</v>
+      </c>
+      <c r="M22" s="29"/>
+    </row>
+    <row r="23" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F23" s="27">
         <v>17</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="29">
         <v>0</v>
       </c>
-      <c r="I23" s="29">
+      <c r="J23" s="31">
+        <v>0</v>
+      </c>
+      <c r="K23" s="29">
         <v>9928.44</v>
       </c>
-    </row>
-    <row r="24" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L23" s="31">
+        <v>7777.25</v>
+      </c>
+      <c r="M23" s="29"/>
+    </row>
+    <row r="24" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F24" s="27">
         <v>18</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I24" s="29">
         <v>0</v>
       </c>
-      <c r="I24" s="29">
+      <c r="J24" s="31">
+        <v>0</v>
+      </c>
+      <c r="K24" s="29">
         <v>10237.66</v>
       </c>
-    </row>
-    <row r="25" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L24" s="31">
+        <v>8019.47</v>
+      </c>
+      <c r="M24" s="29"/>
+    </row>
+    <row r="25" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F25" s="27">
         <v>19</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="29">
         <v>128975.1</v>
       </c>
-      <c r="I25" s="29">
+      <c r="J25" s="31">
+        <v>101299.95</v>
+      </c>
+      <c r="K25" s="29">
         <v>133278.43</v>
       </c>
-    </row>
-    <row r="26" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L25" s="31">
+        <v>104401.09</v>
+      </c>
+      <c r="M25" s="29"/>
+    </row>
+    <row r="26" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F26" s="27">
         <v>20</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G26" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="29">
         <v>1952415.36</v>
       </c>
-      <c r="I26" s="29">
+      <c r="J26" s="31">
+        <v>1952415.36</v>
+      </c>
+      <c r="K26" s="29">
         <v>1957672.69</v>
       </c>
-    </row>
-    <row r="27" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="L26" s="29">
+        <v>1957672.69</v>
+      </c>
+      <c r="M26" s="29"/>
+    </row>
+    <row r="27" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F27" s="27">
         <v>21</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="H27" s="29">
+      <c r="H27" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="I27" s="29">
         <v>72752.28</v>
       </c>
-      <c r="I27" s="29">
+      <c r="J27" s="31">
+        <v>72752.28</v>
+      </c>
+      <c r="K27" s="29">
         <v>72848.81</v>
       </c>
-    </row>
-    <row r="28" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="26"/>
-    </row>
-    <row r="29" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="26"/>
-    </row>
-    <row r="30" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="26"/>
-    </row>
-    <row r="31" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="26"/>
-    </row>
-    <row r="32" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="26"/>
-    </row>
-    <row r="33" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
+      <c r="L27" s="31">
+        <v>72848.81</v>
+      </c>
+      <c r="M27" s="29"/>
+    </row>
+    <row r="28" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I28" s="29"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="29"/>
+    </row>
+    <row r="29" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I29" s="29"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="29"/>
+    </row>
+    <row r="30" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I30" s="29"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="29"/>
+    </row>
+    <row r="31" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I31" s="29"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="29"/>
+    </row>
+    <row r="32" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I32" s="29"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="29"/>
+    </row>
+    <row r="33" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I33" s="26"/>
-    </row>
-    <row r="34" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="26"/>
+    </row>
+    <row r="34" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I34" s="26"/>
-    </row>
-    <row r="35" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="26"/>
+    </row>
+    <row r="35" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I35" s="26"/>
-    </row>
-    <row r="36" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="M35" s="26"/>
+    </row>
+    <row r="36" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I36" s="26"/>
-    </row>
-    <row r="37" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="M36" s="26"/>
+    </row>
+    <row r="37" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I37" s="26"/>
-    </row>
-    <row r="38" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="M37" s="26"/>
+    </row>
+    <row r="38" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I38" s="26"/>
-    </row>
-    <row r="40" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="H40" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="M38" s="26"/>
+    </row>
+    <row r="40" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I40" s="26"/>
-    </row>
-    <row r="42" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="M40" s="26"/>
+    </row>
+    <row r="42" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I42" s="26"/>
-    </row>
-    <row r="43" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-    </row>
-    <row r="46" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="H46" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="M42" s="26"/>
+    </row>
+    <row r="46" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I46" s="26"/>
-    </row>
-    <row r="48" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="M46" s="26"/>
+    </row>
+    <row r="48" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I48" s="26"/>
-    </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
+      <c r="K48" s="26"/>
+      <c r="M48" s="26"/>
     </row>
   </sheetData>
-  <autoFilter ref="F6:I38" xr:uid="{0ED5D522-A34F-425F-A8D2-01DA4E744C0F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F7:I38">
-      <sortCondition ref="F6:F38"/>
+  <autoFilter ref="F6:L27" xr:uid="{82086A02-B839-44CF-B0DE-0C0B01F586C8}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F7:L27">
+      <sortCondition ref="F6:F27"/>
     </sortState>
   </autoFilter>
-  <hyperlinks>
-    <hyperlink ref="G7" r:id="rId1" display="https://app.stashaway.sg/goal/5c62d40bd58ed90007e55db2" xr:uid="{70ABE387-2F06-49A5-AFD8-626CB31FD18A}"/>
-    <hyperlink ref="G8" r:id="rId2" display="https://app.stashaway.sg/goal/681a41ba9b2f2c2b8501bb6e" xr:uid="{260BC53B-85B2-435D-B0CA-427E54B9E9B1}"/>
-    <hyperlink ref="G9" r:id="rId3" display="https://app.stashaway.sg/goal/69aec8761085ac2dc21016ed" xr:uid="{B12740A1-80F0-4458-B548-B8A5230569D7}"/>
-    <hyperlink ref="G10" r:id="rId4" display="https://app.stashaway.sg/goal/69b5552e5f0a07fcc8338b8a" xr:uid="{24317605-01EE-4B0E-9A4A-4C031D687E2A}"/>
-    <hyperlink ref="G11" r:id="rId5" display="https://app.stashaway.sg/goal/69b9919d3915b979131e35be" xr:uid="{AA2D7D19-CE92-4F14-9352-81D108BA8560}"/>
-    <hyperlink ref="G12" r:id="rId6" display="https://app.stashaway.sg/goal/69b992b85f0a07fcc894efa4" xr:uid="{D1F615A7-3A5D-4070-A4EC-097E2716AF5E}"/>
-    <hyperlink ref="G13" r:id="rId7" display="https://app.stashaway.sg/goal/69b99506eb2f9823f9d1225a" xr:uid="{0B3EA2A4-682A-48B8-9A83-C6ED29035A5C}"/>
-    <hyperlink ref="G14" r:id="rId8" display="https://app.stashaway.sg/goal/69e0ca4a2c493b0e78e5e35b" xr:uid="{D3091110-AB7D-4E8B-ABB3-9BC8F079F181}"/>
-    <hyperlink ref="G15" r:id="rId9" display="https://app.stashaway.sg/goal/69e0cc02a16abfe399b9936d" xr:uid="{EEDC9610-A228-44FF-A7EA-1FFEFB6055BB}"/>
-    <hyperlink ref="G16" r:id="rId10" display="https://app.stashaway.sg/goal/69ee569393f415879e429af4" xr:uid="{BE5B0FD5-DE22-4980-AE80-27BEF58AFCFC}"/>
-    <hyperlink ref="G17" r:id="rId11" display="https://app.stashaway.sg/goal/69ee58cf93f415879e42b5c1" xr:uid="{E55813C1-1595-4BC2-B254-69566311A25F}"/>
-    <hyperlink ref="G18" r:id="rId12" display="https://app.stashaway.sg/goal/69f2aef5479f7817d0641742" xr:uid="{F42FC691-6F85-477E-B605-A5643947B903}"/>
-    <hyperlink ref="G19" r:id="rId13" display="https://app.stashaway.sg/goal/6a0df89d5cb1209b659c2b3e" xr:uid="{68439829-6A66-491F-A7A9-0F56A420F17E}"/>
-    <hyperlink ref="G20" r:id="rId14" display="https://app.stashaway.sg/goal/6a0df94c261622dc93333aa1" xr:uid="{07DE6CF9-4367-42F3-9BA0-84093D0F8030}"/>
-    <hyperlink ref="G21" r:id="rId15" display="https://app.stashaway.sg/goal/6a0dfb40261622dc933345b9" xr:uid="{C105A70B-B54A-4493-9919-2B04BB0D2207}"/>
-    <hyperlink ref="G22" r:id="rId16" display="https://app.stashaway.sg/goal/6a0dfb9b23629e305d9c8eaa" xr:uid="{170ADCC9-BF9F-465E-AD4A-50A3E5397B54}"/>
-    <hyperlink ref="G23" r:id="rId17" display="https://app.stashaway.sg/goal/6a1482d1a31c613c4187fbb6" xr:uid="{106B84F1-BF96-4645-B178-B08AEA8A020C}"/>
-    <hyperlink ref="G24" r:id="rId18" display="https://app.stashaway.sg/goal/6a1486d5a31c613c41881936" xr:uid="{FF1EAF78-6A42-4B8B-BD04-00E81B540C73}"/>
-    <hyperlink ref="G25" r:id="rId19" display="https://app.stashaway.sg/goal/652e600df02c35a5183a871e" xr:uid="{3E1C1632-03E7-4CB9-AA16-5CFACE3664F9}"/>
-    <hyperlink ref="G26" r:id="rId20" display="https://app.stashaway.sg/goal/simple/5f17ca30ac0f61000d536b96" xr:uid="{75988D36-5EC3-49E1-BCD8-F239F5360443}"/>
-    <hyperlink ref="G27" r:id="rId21" display="https://app.stashaway.sg/goal/simple/66e9b6efc92a6fb1c008eea7" xr:uid="{F15C5A36-5CBB-4540-A05D-208E5437197D}"/>
-    <hyperlink ref="I7" r:id="rId22" display="https://app.stashaway.sg/goal/5c62d40bd58ed90007e55db2" xr:uid="{56205BB0-8715-4150-BF29-2E40F35569A3}"/>
-    <hyperlink ref="I8" r:id="rId23" display="https://app.stashaway.sg/goal/681a41ba9b2f2c2b8501bb6e" xr:uid="{6BF381F5-EE3E-4EE7-BF0C-CED5201B4558}"/>
-    <hyperlink ref="I9" r:id="rId24" display="https://app.stashaway.sg/goal/69aec8761085ac2dc21016ed" xr:uid="{45F0628D-C173-4B05-AF3C-96D979173C4A}"/>
-    <hyperlink ref="I10" r:id="rId25" display="https://app.stashaway.sg/goal/69b5552e5f0a07fcc8338b8a" xr:uid="{2FD2FDD2-C789-46E4-AEC1-50E509EE2BD5}"/>
-    <hyperlink ref="I11" r:id="rId26" display="https://app.stashaway.sg/goal/69b9919d3915b979131e35be" xr:uid="{10D92E10-08B4-494C-A9F5-9A3678A1D33A}"/>
-    <hyperlink ref="I12" r:id="rId27" display="https://app.stashaway.sg/goal/69b992b85f0a07fcc894efa4" xr:uid="{30820602-B837-4EA2-9FBF-A5B97CEFECA4}"/>
-    <hyperlink ref="I13" r:id="rId28" display="https://app.stashaway.sg/goal/69b99506eb2f9823f9d1225a" xr:uid="{3DE94E4C-500F-47F6-8E64-71100D15DD18}"/>
-    <hyperlink ref="I14" r:id="rId29" display="https://app.stashaway.sg/goal/69e0ca4a2c493b0e78e5e35b" xr:uid="{612464A5-9195-4E4E-A661-5836254F9430}"/>
-    <hyperlink ref="I15" r:id="rId30" display="https://app.stashaway.sg/goal/69e0cc02a16abfe399b9936d" xr:uid="{A71C8159-58A1-4589-9CCD-F75B3739C025}"/>
-    <hyperlink ref="I16" r:id="rId31" display="https://app.stashaway.sg/goal/69ee569393f415879e429af4" xr:uid="{F2A5AE73-2DA8-4F0E-B8B0-4B057071C828}"/>
-    <hyperlink ref="I17" r:id="rId32" display="https://app.stashaway.sg/goal/69ee58cf93f415879e42b5c1" xr:uid="{FF0D79ED-7A70-47A8-916C-1CC856B570AB}"/>
-    <hyperlink ref="I18" r:id="rId33" display="https://app.stashaway.sg/goal/69f2aef5479f7817d0641742" xr:uid="{AA835660-A1D1-489F-9307-BBD62886FABC}"/>
-    <hyperlink ref="I19" r:id="rId34" display="https://app.stashaway.sg/goal/6a0df89d5cb1209b659c2b3e" xr:uid="{FF2DFE51-1935-436C-BA50-FF23B337AE2D}"/>
-    <hyperlink ref="I20" r:id="rId35" display="https://app.stashaway.sg/goal/6a0df94c261622dc93333aa1" xr:uid="{5DACE391-5CCF-45F5-BADF-58B3C02F619B}"/>
-    <hyperlink ref="I21" r:id="rId36" display="https://app.stashaway.sg/goal/6a0dfb40261622dc933345b9" xr:uid="{1BBADA49-7F0D-4006-BA10-FB9B62638414}"/>
-    <hyperlink ref="I22" r:id="rId37" display="https://app.stashaway.sg/goal/6a0dfb9b23629e305d9c8eaa" xr:uid="{9A401E7B-DB64-4CE0-BD17-D71C41500F9B}"/>
-    <hyperlink ref="I23" r:id="rId38" display="https://app.stashaway.sg/goal/6a1482d1a31c613c4187fbb6" xr:uid="{317CA7EF-CC85-4573-AF61-971E5AEF4ABF}"/>
-    <hyperlink ref="I24" r:id="rId39" display="https://app.stashaway.sg/goal/6a1486d5a31c613c41881936" xr:uid="{ACA7DE9F-F360-4E4D-B871-46AF051E7CB4}"/>
-    <hyperlink ref="I25" r:id="rId40" display="https://app.stashaway.sg/goal/652e600df02c35a5183a871e" xr:uid="{0A7A7F5C-E295-4693-A845-62B9222BBE84}"/>
-    <hyperlink ref="I26" r:id="rId41" display="https://app.stashaway.sg/goal/simple/5f17ca30ac0f61000d536b96" xr:uid="{7E51EACB-46EF-4524-B057-1ED509BD04C5}"/>
-    <hyperlink ref="I27" r:id="rId42" display="https://app.stashaway.sg/goal/simple/66e9b6efc92a6fb1c008eea7" xr:uid="{61C60832-4D2C-4E13-A6DB-B1335928577C}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82086A02-B839-44CF-B0DE-0C0B01F586C8}">
-  <dimension ref="F6:I27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="7" max="7" width="31.85546875" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="6" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F6" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="I6" s="33">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="7" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F7" s="27">
-        <v>1</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I7" s="32">
-        <v>386042.44</v>
-      </c>
-    </row>
-    <row r="8" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F8" s="27">
-        <v>2</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I8" s="32">
-        <v>51511.93</v>
-      </c>
-    </row>
-    <row r="9" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F9" s="27">
-        <v>3</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I9" s="32">
-        <v>7757.91</v>
-      </c>
-    </row>
-    <row r="10" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F10" s="27">
-        <v>4</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I10" s="32">
-        <v>274770.03999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F11" s="27">
-        <v>5</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I11" s="32">
-        <v>20142.27</v>
-      </c>
-    </row>
-    <row r="12" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F12" s="27">
-        <v>6</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I12" s="32">
-        <v>3710.2</v>
-      </c>
-    </row>
-    <row r="13" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F13" s="27">
-        <v>7</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I13" s="32">
-        <v>5043.68</v>
-      </c>
-    </row>
-    <row r="14" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F14" s="27">
-        <v>8</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="32">
-        <v>20109.849999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F15" s="27">
-        <v>9</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I15" s="32">
-        <v>8239.41</v>
-      </c>
-    </row>
-    <row r="16" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F16" s="27">
-        <v>10</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I16" s="32">
-        <v>24164.27</v>
-      </c>
-    </row>
-    <row r="17" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F17" s="27">
-        <v>11</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I17" s="32">
-        <v>8163.64</v>
-      </c>
-    </row>
-    <row r="18" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F18" s="27">
-        <v>12</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I18" s="32">
-        <v>41022.49</v>
-      </c>
-    </row>
-    <row r="19" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F19" s="27">
-        <v>13</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I19" s="32">
-        <v>7963.59</v>
-      </c>
-    </row>
-    <row r="20" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F20" s="27">
-        <v>14</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I20" s="32">
-        <v>8197.0300000000007</v>
-      </c>
-    </row>
-    <row r="21" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F21" s="27">
-        <v>15</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I21" s="32">
-        <v>7783.46</v>
-      </c>
-    </row>
-    <row r="22" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F22" s="27">
-        <v>16</v>
-      </c>
-      <c r="G22" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I22" s="32">
-        <v>9988.9500000000007</v>
-      </c>
-    </row>
-    <row r="23" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F23" s="27">
-        <v>17</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I23" s="32">
-        <v>7777.25</v>
-      </c>
-    </row>
-    <row r="24" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F24" s="27">
-        <v>18</v>
-      </c>
-      <c r="G24" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I24" s="32">
-        <v>8019.47</v>
-      </c>
-    </row>
-    <row r="25" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F25" s="27">
-        <v>19</v>
-      </c>
-      <c r="G25" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="I25" s="32">
-        <v>104401.09</v>
-      </c>
-    </row>
-    <row r="26" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F26" s="27">
-        <v>20</v>
-      </c>
-      <c r="G26" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="H26" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I26" s="32">
-        <v>1962672.69</v>
-      </c>
-    </row>
-    <row r="27" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F27" s="27">
-        <v>21</v>
-      </c>
-      <c r="G27" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I27" s="32">
-        <v>72848.81</v>
-      </c>
-    </row>
-  </sheetData>
   <hyperlinks>
     <hyperlink ref="G7" r:id="rId1" display="https://app.stashaway.sg/goal/5c62d40bd58ed90007e55db2" xr:uid="{B8410F5F-B52A-43FE-AD57-09699312FF39}"/>
     <hyperlink ref="G8" r:id="rId2" display="https://app.stashaway.sg/goal/681a41ba9b2f2c2b8501bb6e" xr:uid="{DBCE38D2-936A-4932-987D-396F8DA16168}"/>
@@ -5586,35 +5511,56 @@
     <hyperlink ref="G25" r:id="rId19" display="https://app.stashaway.sg/goal/652e600df02c35a5183a871e" xr:uid="{5A4E2E56-9E96-4FD1-A436-2FC62E68C435}"/>
     <hyperlink ref="G26" r:id="rId20" display="https://app.stashaway.sg/goal/simple/5f17ca30ac0f61000d536b96" xr:uid="{1D06BF62-D98A-47E1-A6A3-48F77D8C849F}"/>
     <hyperlink ref="G27" r:id="rId21" display="https://app.stashaway.sg/goal/simple/66e9b6efc92a6fb1c008eea7" xr:uid="{483A236E-CF39-455E-A03A-83027C9D7F12}"/>
-    <hyperlink ref="I7" r:id="rId22" display="https://app.stashaway.sg/goal/5c62d40bd58ed90007e55db2" xr:uid="{C17D72ED-8820-432C-878E-AA076FE9A30D}"/>
-    <hyperlink ref="I8" r:id="rId23" display="https://app.stashaway.sg/goal/681a41ba9b2f2c2b8501bb6e" xr:uid="{0BA95CE5-E875-4E87-B4D1-41BD83268001}"/>
-    <hyperlink ref="I9" r:id="rId24" display="https://app.stashaway.sg/goal/69aec8761085ac2dc21016ed" xr:uid="{13D5FFC7-FC04-4BC9-B1C2-2AF42262342A}"/>
-    <hyperlink ref="I10" r:id="rId25" display="https://app.stashaway.sg/goal/69b5552e5f0a07fcc8338b8a" xr:uid="{28E20DE7-AF1F-4180-817D-8F964C0416CD}"/>
-    <hyperlink ref="I11" r:id="rId26" display="https://app.stashaway.sg/goal/69b9919d3915b979131e35be" xr:uid="{91FF877E-B6A3-45F3-9733-97E4BCEBB2F1}"/>
-    <hyperlink ref="I12" r:id="rId27" display="https://app.stashaway.sg/goal/69b992b85f0a07fcc894efa4" xr:uid="{C20C8B70-DEF3-46A2-AAF5-CEB7787E1517}"/>
-    <hyperlink ref="I13" r:id="rId28" display="https://app.stashaway.sg/goal/69b99506eb2f9823f9d1225a" xr:uid="{7566B43A-FFCF-4DFB-A670-BF007E61B7CA}"/>
-    <hyperlink ref="I14" r:id="rId29" display="https://app.stashaway.sg/goal/69e0ca4a2c493b0e78e5e35b" xr:uid="{D7719B9A-9816-4DC4-958E-AFE0AA636DB2}"/>
-    <hyperlink ref="I15" r:id="rId30" display="https://app.stashaway.sg/goal/69e0cc02a16abfe399b9936d" xr:uid="{F1BAEEBE-8980-42B7-ACF3-C8820DD58501}"/>
-    <hyperlink ref="I16" r:id="rId31" display="https://app.stashaway.sg/goal/69ee569393f415879e429af4" xr:uid="{ACA9994E-DEDD-476E-A456-40BA014713E0}"/>
-    <hyperlink ref="I17" r:id="rId32" display="https://app.stashaway.sg/goal/69ee58cf93f415879e42b5c1" xr:uid="{4E8DCEF2-20BD-4C1E-B92B-E187C49FD39B}"/>
-    <hyperlink ref="I18" r:id="rId33" display="https://app.stashaway.sg/goal/69f2aef5479f7817d0641742" xr:uid="{1D80337B-84EB-4649-8250-AAB175198730}"/>
-    <hyperlink ref="I19" r:id="rId34" display="https://app.stashaway.sg/goal/6a0df89d5cb1209b659c2b3e" xr:uid="{5C47BEB0-7C1A-46F3-B7C8-554640A045D2}"/>
-    <hyperlink ref="I20" r:id="rId35" display="https://app.stashaway.sg/goal/6a0df94c261622dc93333aa1" xr:uid="{7CFD4CA6-80A4-4686-91A9-0EA2807464E3}"/>
-    <hyperlink ref="I21" r:id="rId36" display="https://app.stashaway.sg/goal/6a0dfb40261622dc933345b9" xr:uid="{4CDCA4B2-256A-4B14-9EB6-B434A2C66081}"/>
-    <hyperlink ref="I22" r:id="rId37" display="https://app.stashaway.sg/goal/6a0dfb9b23629e305d9c8eaa" xr:uid="{EA1B4797-2246-4353-937D-FC560A66A7BF}"/>
-    <hyperlink ref="I23" r:id="rId38" display="https://app.stashaway.sg/goal/6a1482d1a31c613c4187fbb6" xr:uid="{41B40BDC-953A-4244-B40D-1617966F4CCB}"/>
-    <hyperlink ref="I24" r:id="rId39" display="https://app.stashaway.sg/goal/6a1486d5a31c613c41881936" xr:uid="{8D83F18D-CEDD-4E68-8732-4ED8F98618B0}"/>
-    <hyperlink ref="I25" r:id="rId40" display="https://app.stashaway.sg/goal/652e600df02c35a5183a871e" xr:uid="{12E0D934-4A36-4341-8DEA-A7A618F9F345}"/>
-    <hyperlink ref="I26" r:id="rId41" display="https://app.stashaway.sg/goal/simple/5f17ca30ac0f61000d536b96" xr:uid="{850BEC22-62FD-493D-A386-C681D62134A3}"/>
-    <hyperlink ref="I27" r:id="rId42" display="https://app.stashaway.sg/goal/simple/66e9b6efc92a6fb1c008eea7" xr:uid="{01139CE9-0C63-4F90-9B75-0CACB36493B2}"/>
+    <hyperlink ref="L7" r:id="rId22" display="https://app.stashaway.sg/goal/5c62d40bd58ed90007e55db2" xr:uid="{C17D72ED-8820-432C-878E-AA076FE9A30D}"/>
+    <hyperlink ref="L8" r:id="rId23" display="https://app.stashaway.sg/goal/681a41ba9b2f2c2b8501bb6e" xr:uid="{0BA95CE5-E875-4E87-B4D1-41BD83268001}"/>
+    <hyperlink ref="L9" r:id="rId24" display="https://app.stashaway.sg/goal/69aec8761085ac2dc21016ed" xr:uid="{13D5FFC7-FC04-4BC9-B1C2-2AF42262342A}"/>
+    <hyperlink ref="L10" r:id="rId25" display="https://app.stashaway.sg/goal/69b5552e5f0a07fcc8338b8a" xr:uid="{28E20DE7-AF1F-4180-817D-8F964C0416CD}"/>
+    <hyperlink ref="L11" r:id="rId26" display="https://app.stashaway.sg/goal/69b9919d3915b979131e35be" xr:uid="{91FF877E-B6A3-45F3-9733-97E4BCEBB2F1}"/>
+    <hyperlink ref="L12" r:id="rId27" display="https://app.stashaway.sg/goal/69b992b85f0a07fcc894efa4" xr:uid="{C20C8B70-DEF3-46A2-AAF5-CEB7787E1517}"/>
+    <hyperlink ref="L13" r:id="rId28" display="https://app.stashaway.sg/goal/69b99506eb2f9823f9d1225a" xr:uid="{7566B43A-FFCF-4DFB-A670-BF007E61B7CA}"/>
+    <hyperlink ref="L14" r:id="rId29" display="https://app.stashaway.sg/goal/69e0ca4a2c493b0e78e5e35b" xr:uid="{D7719B9A-9816-4DC4-958E-AFE0AA636DB2}"/>
+    <hyperlink ref="L15" r:id="rId30" display="https://app.stashaway.sg/goal/69e0cc02a16abfe399b9936d" xr:uid="{F1BAEEBE-8980-42B7-ACF3-C8820DD58501}"/>
+    <hyperlink ref="L16" r:id="rId31" display="https://app.stashaway.sg/goal/69ee569393f415879e429af4" xr:uid="{ACA9994E-DEDD-476E-A456-40BA014713E0}"/>
+    <hyperlink ref="L17" r:id="rId32" display="https://app.stashaway.sg/goal/69ee58cf93f415879e42b5c1" xr:uid="{4E8DCEF2-20BD-4C1E-B92B-E187C49FD39B}"/>
+    <hyperlink ref="L18" r:id="rId33" display="https://app.stashaway.sg/goal/69f2aef5479f7817d0641742" xr:uid="{1D80337B-84EB-4649-8250-AAB175198730}"/>
+    <hyperlink ref="L19" r:id="rId34" display="https://app.stashaway.sg/goal/6a0df89d5cb1209b659c2b3e" xr:uid="{5C47BEB0-7C1A-46F3-B7C8-554640A045D2}"/>
+    <hyperlink ref="L20" r:id="rId35" display="https://app.stashaway.sg/goal/6a0df94c261622dc93333aa1" xr:uid="{7CFD4CA6-80A4-4686-91A9-0EA2807464E3}"/>
+    <hyperlink ref="L21" r:id="rId36" display="https://app.stashaway.sg/goal/6a0dfb40261622dc933345b9" xr:uid="{4CDCA4B2-256A-4B14-9EB6-B434A2C66081}"/>
+    <hyperlink ref="L22" r:id="rId37" display="https://app.stashaway.sg/goal/6a0dfb9b23629e305d9c8eaa" xr:uid="{EA1B4797-2246-4353-937D-FC560A66A7BF}"/>
+    <hyperlink ref="L23" r:id="rId38" display="https://app.stashaway.sg/goal/6a1482d1a31c613c4187fbb6" xr:uid="{41B40BDC-953A-4244-B40D-1617966F4CCB}"/>
+    <hyperlink ref="L24" r:id="rId39" display="https://app.stashaway.sg/goal/6a1486d5a31c613c41881936" xr:uid="{8D83F18D-CEDD-4E68-8732-4ED8F98618B0}"/>
+    <hyperlink ref="L25" r:id="rId40" display="https://app.stashaway.sg/goal/652e600df02c35a5183a871e" xr:uid="{12E0D934-4A36-4341-8DEA-A7A618F9F345}"/>
+    <hyperlink ref="L27" r:id="rId41" display="https://app.stashaway.sg/goal/simple/66e9b6efc92a6fb1c008eea7" xr:uid="{01139CE9-0C63-4F90-9B75-0CACB36493B2}"/>
+    <hyperlink ref="K7" r:id="rId42" display="https://app.stashaway.sg/goal/5c62d40bd58ed90007e55db2" xr:uid="{ECD7872D-6E65-49C9-8B32-1E6AB33534CE}"/>
+    <hyperlink ref="K8" r:id="rId43" display="https://app.stashaway.sg/goal/681a41ba9b2f2c2b8501bb6e" xr:uid="{B66045AC-5EB7-40FE-AACD-8FC326A6933C}"/>
+    <hyperlink ref="K9" r:id="rId44" display="https://app.stashaway.sg/goal/69aec8761085ac2dc21016ed" xr:uid="{97ED010E-98AC-4B50-B901-335D42D1B80C}"/>
+    <hyperlink ref="K10" r:id="rId45" display="https://app.stashaway.sg/goal/69b5552e5f0a07fcc8338b8a" xr:uid="{CA6B34CF-276C-4CC7-9267-A64472D77515}"/>
+    <hyperlink ref="K11" r:id="rId46" display="https://app.stashaway.sg/goal/69b9919d3915b979131e35be" xr:uid="{610B8FFF-8957-4686-B608-1029310CFE0C}"/>
+    <hyperlink ref="K12" r:id="rId47" display="https://app.stashaway.sg/goal/69b992b85f0a07fcc894efa4" xr:uid="{59C6D570-D7D4-4EEE-8337-1719F99D609B}"/>
+    <hyperlink ref="K13" r:id="rId48" display="https://app.stashaway.sg/goal/69b99506eb2f9823f9d1225a" xr:uid="{C7B6D8E1-8419-4136-9081-CF1F5B455CC9}"/>
+    <hyperlink ref="K14" r:id="rId49" display="https://app.stashaway.sg/goal/69e0ca4a2c493b0e78e5e35b" xr:uid="{707BA807-07AD-413A-9772-A74C2F60150E}"/>
+    <hyperlink ref="K15" r:id="rId50" display="https://app.stashaway.sg/goal/69e0cc02a16abfe399b9936d" xr:uid="{EAB4FB4C-C866-441C-BE6D-BC1BDADB6D05}"/>
+    <hyperlink ref="K16" r:id="rId51" display="https://app.stashaway.sg/goal/69ee569393f415879e429af4" xr:uid="{386CD5B2-C28C-4A7B-A09B-17CE5C0A34C6}"/>
+    <hyperlink ref="K17" r:id="rId52" display="https://app.stashaway.sg/goal/69ee58cf93f415879e42b5c1" xr:uid="{CE050D7E-7B74-4452-AD3B-08265500BA3F}"/>
+    <hyperlink ref="K18" r:id="rId53" display="https://app.stashaway.sg/goal/69f2aef5479f7817d0641742" xr:uid="{1166158F-D7CF-41E8-9564-CA0F82DC3B43}"/>
+    <hyperlink ref="K19" r:id="rId54" display="https://app.stashaway.sg/goal/6a0df89d5cb1209b659c2b3e" xr:uid="{D8E3A26D-6B3E-49EF-A1F3-983970C794CB}"/>
+    <hyperlink ref="K20" r:id="rId55" display="https://app.stashaway.sg/goal/6a0df94c261622dc93333aa1" xr:uid="{9B7E8A4A-16F4-4B59-877D-1406D21380FC}"/>
+    <hyperlink ref="K21" r:id="rId56" display="https://app.stashaway.sg/goal/6a0dfb40261622dc933345b9" xr:uid="{6DCD9C6A-1032-42F8-B751-4366BEBC42E7}"/>
+    <hyperlink ref="K22" r:id="rId57" display="https://app.stashaway.sg/goal/6a0dfb9b23629e305d9c8eaa" xr:uid="{74AD6852-7860-42B2-8FFC-534FCCF6804B}"/>
+    <hyperlink ref="K23" r:id="rId58" display="https://app.stashaway.sg/goal/6a1482d1a31c613c4187fbb6" xr:uid="{76580083-540B-4186-A7E7-11B16439AD79}"/>
+    <hyperlink ref="K24" r:id="rId59" display="https://app.stashaway.sg/goal/6a1486d5a31c613c41881936" xr:uid="{83F56B8F-56EA-4F59-87E9-F862966F9734}"/>
+    <hyperlink ref="K25" r:id="rId60" display="https://app.stashaway.sg/goal/652e600df02c35a5183a871e" xr:uid="{0A1283AC-2E56-4DAE-BEE5-AD83CE6D94F5}"/>
+    <hyperlink ref="K27" r:id="rId61" display="https://app.stashaway.sg/goal/simple/66e9b6efc92a6fb1c008eea7" xr:uid="{5EECE4F9-B1E5-44CD-8E42-2766ADB0E611}"/>
+    <hyperlink ref="K26" r:id="rId62" display="https://app.stashaway.sg/goal/simple/5f17ca30ac0f61000d536b96" xr:uid="{1DE5F0E2-3132-4A6E-AF91-3680AC5CDB10}"/>
+    <hyperlink ref="L26" r:id="rId63" display="https://app.stashaway.sg/goal/simple/5f17ca30ac0f61000d536b96" xr:uid="{3EC6EB23-0F6A-4F72-B403-942E8BEC56A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5622,9 +5568,10 @@
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>160</v>
       </c>
@@ -5640,8 +5587,11 @@
       <c r="E1" s="23" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="23" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
         <v>46140</v>
       </c>
@@ -5657,8 +5607,11 @@
       <c r="E2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="24">
         <v>46142</v>
       </c>
@@ -5674,8 +5627,11 @@
       <c r="E3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
         <v>46143</v>
       </c>
@@ -5692,7 +5648,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
         <v>46143</v>
       </c>
@@ -5709,7 +5665,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
         <v>46143</v>
       </c>
@@ -5725,8 +5681,11 @@
       <c r="E6" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24">
         <v>46160</v>
       </c>
@@ -5742,8 +5701,11 @@
       <c r="E7" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="24">
         <v>46163</v>
       </c>
@@ -5760,7 +5722,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="24">
         <v>46163</v>
       </c>
@@ -5776,8 +5738,11 @@
       <c r="E9" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="36">
+        <v>0.77910000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <v>46163</v>
       </c>
@@ -5794,7 +5759,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <v>46163</v>
       </c>
@@ -5811,7 +5776,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
         <v>46167</v>
       </c>
@@ -5827,8 +5792,11 @@
       <c r="E12" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
         <v>46168</v>
       </c>
@@ -5844,8 +5812,11 @@
       <c r="E13" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>0.78129999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
         <v>46168</v>
       </c>
@@ -5861,8 +5832,11 @@
       <c r="E14" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>0.78129999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="24">
         <v>46170</v>
       </c>
@@ -5878,9 +5852,32 @@
       <c r="E15" t="s">
         <v>169</v>
       </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="24">
+        <v>46174</v>
+      </c>
+      <c r="B16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="37">
+        <v>5000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E14" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <autoFilter ref="A1:E16" xr:uid="{00000000-0001-0000-0300-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E15">
       <sortCondition ref="A1:A14"/>
     </sortState>

--- a/data/holding.xlsx
+++ b/data/holding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dalva\src\project-hail-mary\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639C7904-62E6-4364-9805-08629C687371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAE625C-2D4B-4E50-873C-2198690325BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41850" yWindow="2520" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="1335" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Holdings" sheetId="1" r:id="rId1"/>
@@ -768,7 +768,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -935,12 +935,6 @@
       <name val="Noto Sans"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="Noto Sans"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -970,7 +964,7 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1039,7 +1033,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -5721,8 +5714,11 @@
       <c r="E8" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
         <v>46163</v>
       </c>
@@ -5738,7 +5734,7 @@
       <c r="E9" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9">
         <v>0.77910000000000001</v>
       </c>
     </row>
@@ -5758,6 +5754,9 @@
       <c r="E10" t="s">
         <v>168</v>
       </c>
+      <c r="F10">
+        <v>0.77910000000000001</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
@@ -5775,6 +5774,9 @@
       <c r="E11" t="s">
         <v>168</v>
       </c>
+      <c r="F11">
+        <v>0.77910000000000001</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
@@ -5866,7 +5868,7 @@
       <c r="C16" t="s">
         <v>159</v>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="36">
         <v>5000</v>
       </c>
       <c r="E16" t="s">
